--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1239,7 +1239,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1421,7 +1421,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1492,7 +1492,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
@@ -1746,7 +1746,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2108,7 +2108,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="69.21875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3406" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3407" uniqueCount="567">
   <si>
     <t>Property</t>
   </si>
@@ -1318,7 +1318,13 @@
     <t>ICD-11</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationPhysicalExamBodySite_VS</t>
+    <t>example</t>
+  </si>
+  <si>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1535,9 +1541,6 @@
   </si>
   <si>
     <t>適切な解釈のためにターゲット母集団を特定できる必要があります。 / Need to be able to identify the target population for proper interpretation.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
@@ -2109,7 +2112,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.21875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.94921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -8346,11 +8349,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8386,27 +8391,27 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8432,16 +8437,16 @@
         <v>188</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8470,7 +8475,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8488,7 +8493,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8509,10 +8514,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8523,10 +8528,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8549,16 +8554,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8608,7 +8613,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8626,27 +8631,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8669,16 +8674,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8728,7 +8733,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8746,27 +8751,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8789,19 +8794,19 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8850,7 +8855,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8862,7 +8867,7 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
@@ -8871,10 +8876,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8885,10 +8890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9003,10 +9008,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9123,14 +9128,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9152,10 +9157,10 @@
         <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>143</v>
@@ -9210,7 +9215,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9245,10 +9250,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9271,13 +9276,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9328,7 +9333,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9337,7 +9342,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9349,10 +9354,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9363,10 +9368,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9389,13 +9394,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9446,7 +9451,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9455,7 +9460,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9467,10 +9472,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9481,10 +9486,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9510,16 +9515,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9547,10 +9552,10 @@
         <v>118</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9568,7 +9573,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9586,10 +9591,10 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>407</v>
@@ -9603,10 +9608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9632,16 +9637,16 @@
         <v>188</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9666,13 +9671,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9690,7 +9695,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9708,10 +9713,10 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>407</v>
@@ -9725,10 +9730,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9751,17 +9756,17 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9810,7 +9815,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9834,7 +9839,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9845,10 +9850,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9874,10 +9879,10 @@
         <v>206</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9928,7 +9933,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9949,10 +9954,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9963,10 +9968,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9989,16 +9994,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10048,7 +10053,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10069,10 +10074,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10083,10 +10088,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10109,16 +10114,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10168,7 +10173,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10189,10 +10194,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10203,10 +10208,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10229,19 +10234,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10290,7 +10295,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10311,10 +10316,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10325,10 +10330,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10443,10 +10448,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10563,14 +10568,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10592,10 +10597,10 @@
         <v>140</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>143</v>
@@ -10650,7 +10655,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10685,10 +10690,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10714,13 +10719,13 @@
         <v>188</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>289</v>
@@ -10770,7 +10775,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>94</v>
@@ -10788,7 +10793,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>293</v>
@@ -10805,10 +10810,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10923,10 +10928,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11043,10 +11048,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11163,10 +11168,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>302</v>
@@ -11285,10 +11290,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11403,10 +11408,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11523,10 +11528,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11645,10 +11650,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11765,10 +11770,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11808,7 +11813,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>83</v>
@@ -11885,10 +11890,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11931,7 +11936,7 @@
         <v>83</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>83</v>
@@ -12005,10 +12010,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12127,10 +12132,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12249,10 +12254,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12278,13 +12283,13 @@
         <v>375</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>378</v>
@@ -12336,7 +12341,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12354,7 +12359,7 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>382</v>
@@ -12371,10 +12376,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12400,13 +12405,13 @@
         <v>188</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>392</v>
@@ -12458,7 +12463,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12493,10 +12498,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12522,16 +12527,16 @@
         <v>188</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12580,7 +12585,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12615,10 +12620,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12644,16 +12649,16 @@
         <v>84</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12702,7 +12707,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12723,10 +12728,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
